--- a/output/pdf_financials_xlsx/AUMC.xlsx
+++ b/output/pdf_financials_xlsx/AUMC.xlsx
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.222497</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.067661</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.190145</v>
       </c>
     </row>
     <row r="35">
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.222497</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.067661</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.190145</v>
       </c>
     </row>
     <row r="37">
@@ -1259,10 +1259,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.06779499999999999</v>
+        <v>0.000134</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.263643</v>
+        <v>0.07349799999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/AUMC.xlsx
+++ b/output/pdf_financials_xlsx/AUMC.xlsx
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0</v>
+        <v>0.006986</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0</v>
+        <v>0.006986</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>0</v>
@@ -1608,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0</v>
+        <v>0.15995</v>
       </c>
     </row>
     <row r="70">
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.15995</v>
       </c>
     </row>
     <row r="72">
@@ -1704,7 +1704,7 @@
         <v>0.081486</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.15995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1789,10 +1789,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D80" s="3" t="n">
+        <v>0.06204836009229475</v>
       </c>
     </row>
     <row r="81">
@@ -1916,10 +1914,10 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>0.0529</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>0.4315</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>0</v>
@@ -1980,7 +1978,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.3661</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0</v>
@@ -2982,7 +2980,11 @@
           <t>Due to related party Note 6, 11</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -3044,7 +3046,11 @@
           <t>Loan payable Note 7</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3420,7 +3426,11 @@
           <t>Due to related party Note 8</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>0.006986</v>
       </c>
@@ -3544,7 +3554,11 @@
           <t>Share capital Note 5</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.0529</v>
       </c>
@@ -3573,7 +3587,11 @@
           <t>Warrant reserve Note 7</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>0.3661</v>
       </c>
